--- a/AAII_Financials/Quarterly/KNF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
   <si>
     <t>KNF</t>
   </si>
@@ -656,287 +656,300 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>938600</v>
+      </c>
+      <c r="E8" s="3">
         <v>410100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>755100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1203700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>833800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>353500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>657200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1105300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>806900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>329600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>646900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1090400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>785200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>307900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>537500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>975400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>711800</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>775800</v>
+      </c>
+      <c r="E9" s="3">
         <v>412900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>613000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>917600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>676500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>363100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>543100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>832300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>630700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>323100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>534400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>821000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>632200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>303800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>465600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>790900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>608500</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>162800</v>
+      </c>
+      <c r="E10" s="3">
         <v>-2800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>142000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>286100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>157200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-9600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>114100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>273000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>176200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>112500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>269400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>153000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>71900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>184500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>103300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,8 +972,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1021,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,52 +1100,55 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1800</v>
       </c>
-      <c r="G14" s="3">
-        <v>-3700</v>
-      </c>
       <c r="H14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I14" s="3">
         <v>1800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>10500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1145,53 +1165,56 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E15" s="3">
         <v>52200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>51300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>53500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>50200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>38800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>35400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>34800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>34500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>31300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>31800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>31100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>29600</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>856000</v>
+      </c>
+      <c r="E17" s="3">
         <v>494400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>691900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>985600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>744100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>430800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>604300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>896100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>689700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>382500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>597200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>878900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>691700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>352500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>501900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>832500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>651400</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-84200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>63200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>218100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>89700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-77400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>52900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>209200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>117200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-52900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>49700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>211500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>93500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-44600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>35600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>142900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>60400</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,318 +1409,334 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
-        <v>3100</v>
-      </c>
       <c r="H20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6700</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2800</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>139200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-32700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>115600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>271000</v>
       </c>
-      <c r="G21" s="3">
-        <v>136700</v>
-      </c>
       <c r="H21" s="3">
+        <v>140300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-37600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>89300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>243300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>152500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>87700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>243200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>124900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>65500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>172100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>87300</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E22" s="3">
         <v>20700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>21300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>23000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>15300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>13900</v>
       </c>
       <c r="K22" s="3">
         <v>13900</v>
       </c>
       <c r="L22" s="3">
+        <v>13900</v>
+      </c>
+      <c r="M22" s="3">
         <v>14000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>15400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7400</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-107600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>45200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>193400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>67900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-93300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>33100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>197700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>104100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-64000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>26800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>194900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>76900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-53200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>27700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>132800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>50100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-28400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>50200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>17300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-24600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>49600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>26200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-16300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>48200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>20000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>33200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11600</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-79200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>32000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>143200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>50600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-68700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>23300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>148100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>77900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-47600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>146700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>56800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-41300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>99700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>38600</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-79200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>32000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>143200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>50600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-68700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>23300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>148100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>77900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-47600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>146700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>56800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-41300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>99700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>38600</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,132 +2187,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
-        <v>-3100</v>
-      </c>
       <c r="H32" s="3">
+        <v>400</v>
+      </c>
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6700</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2800</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-79200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>32000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>143200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>50600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-68700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>23300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>148100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>77900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-47600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>20700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>146700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>56800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-41300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>99700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>38600</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-79200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>32000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>143200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>50600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-68700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>23300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>148100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>77900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-47600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>20700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>146700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>56800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-41300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>99700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>38600</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,53 +2569,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E41" s="3">
         <v>13300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>73800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>86100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>236800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>220400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>170700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>219300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>116200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>68500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2632,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2607,53 +2697,56 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>590300</v>
+      </c>
+      <c r="E43" s="3">
         <v>304500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>355600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>584700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>492100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>266600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>298500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>518500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>472100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>217300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>294100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>542400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>476600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>222400</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2669,53 +2762,56 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>507300</v>
+      </c>
+      <c r="E44" s="3">
         <v>480500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>435700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>436500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>479500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>467100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>380300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>347300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>385400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>375800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>319600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>314700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>374400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>373200</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2731,8 +2827,11 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2793,53 +2892,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1271700</v>
+      </c>
+      <c r="E46" s="3">
         <v>942300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>960900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1135300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1103300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>946700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>987700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1159600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>949700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>817800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>913500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1011400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>958300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>639200</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,53 +2957,56 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E47" s="3">
         <v>56300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>55300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>53800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>52600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>52500</v>
-      </c>
-      <c r="I47" s="3">
-        <v>45800</v>
       </c>
       <c r="J47" s="3">
         <v>45800</v>
       </c>
       <c r="K47" s="3">
+        <v>45800</v>
+      </c>
+      <c r="L47" s="3">
         <v>44600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>44700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>41200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>39700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>40600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>38900</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2917,53 +3022,56 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2228100</v>
+      </c>
+      <c r="E48" s="3">
         <v>2208000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2081500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2011400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1973300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1790000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1491100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1393600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1403200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1366400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1359800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1343800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1357400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1361400</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,53 +3087,56 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>617700</v>
+      </c>
+      <c r="E49" s="3">
         <v>611200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>552300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>502800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>502300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>491500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>326600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>285100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>285400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>284800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>285300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>285900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>286600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>287300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,8 +3282,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3209,8 +3329,8 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,53 +3412,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4177800</v>
+      </c>
+      <c r="E54" s="3">
         <v>3817900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3650100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3703300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3631500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3280700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2851200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2884100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2682900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2513600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2599800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2680900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2642900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2326800</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,53 +3529,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>227900</v>
+      </c>
+      <c r="E57" s="3">
         <v>131400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>145600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>211200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>172200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>112000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>140800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>180600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>164200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>97400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>107700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>149000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>174600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>80400</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3461,53 +3592,56 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E58" s="3">
         <v>27300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>27700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>26500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>26100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>25200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>25300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>22300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>20700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>20400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>20800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>21100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>251200</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3523,53 +3657,56 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E59" s="3">
         <v>44600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>59200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>71500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>54300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>56200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>57500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>60800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>60700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>50800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>67600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>112100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>74500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>60900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,53 +3722,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>477200</v>
+      </c>
+      <c r="E60" s="3">
         <v>352300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>378000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>474400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>397200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>322100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>370000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>426100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>378300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>297200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>347300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>425000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>384400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>473200</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,53 +3787,56 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1634900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1455600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1190500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1211200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1376000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1193500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>701400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>703600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>706700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>706100</v>
-      </c>
-      <c r="M61" s="3">
-        <v>706300</v>
       </c>
       <c r="N61" s="3">
         <v>706300</v>
       </c>
       <c r="O61" s="3">
+        <v>706300</v>
+      </c>
+      <c r="P61" s="3">
         <v>863900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>609400</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3709,53 +3852,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>163300</v>
+      </c>
+      <c r="E62" s="3">
         <v>158300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>136900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>146300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>139700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>136000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>115100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>117600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>120000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>117600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>88400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>132700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>129300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>94300</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,53 +4112,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2571900</v>
+      </c>
+      <c r="E66" s="3">
         <v>2258500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2009200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2096100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2170300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1873100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1375100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1435200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1384200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1295000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1333800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1437900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1548000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1352000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,53 +4462,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>989300</v>
+      </c>
+      <c r="E72" s="3">
         <v>945400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1024600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>992600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>849400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>798800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>867500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>844300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>696200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>618200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>665900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>645200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>498500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>441700</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,53 +4722,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1605900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1559300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1640900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1607200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1461100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1407600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1476100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1448900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1298700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1218600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1266000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1243000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1094900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>974800</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-79200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>32000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>143200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>50600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-68700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>23300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>148100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>77900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-47600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>20700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>146700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>56800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-41300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>99700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>38600</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,70 +5014,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E83" s="3">
         <v>37700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>31100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>34300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>34000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>31700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>28100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>31100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>30500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>29000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>26400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>29800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>29000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>27700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>29200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>30500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>29800</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-75100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-58600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>195900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>250400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-42600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-125300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>172400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>239700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-46600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-43200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>182800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>223300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-79300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>168000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>187200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-71600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,70 +5494,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-72900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-77300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-57700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-61700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-153600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-75000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-45300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-23500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-59900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-43700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-37800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-24200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-42400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-56300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-41600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-39500</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,70 +5687,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-81500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-251100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-130600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-81100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-198300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-503600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-157000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-65100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-45100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-34900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-23400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-40800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-38000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-39800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-37800</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5590,8 +5824,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,28 +6037,31 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>183200</v>
+      </c>
+      <c r="E100" s="3">
         <v>261600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-22900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-165900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>180100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>486300</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-1800</v>
       </c>
       <c r="J100" s="3">
         <v>-1800</v>
@@ -5824,40 +6070,43 @@
         <v>-1800</v>
       </c>
       <c r="L100" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="M100" s="3">
         <v>-3400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-156800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>75700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>117200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-139000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-141100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>110200</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5900,8 +6149,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -5918,66 +6167,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-48000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>42300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-60800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-142700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>210300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-113500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-91700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>146200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>47700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>61300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>700</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
